--- a/04-templates/files/02-payer-priority-matrix.xlsx
+++ b/04-templates/files/02-payer-priority-matrix.xlsx
@@ -633,7 +633,7 @@
     <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PAYER PRIORITY MATRIX  ·  The Marketing Pros</t>
+          <t>PAYER PRIORITY MATRIX  ·  Riverside Medical Group  (Sample)</t>
         </is>
       </c>
     </row>
